--- a/08_tables/q8_twfe_full_correlation_matrix.xlsx
+++ b/08_tables/q8_twfe_full_correlation_matrix.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q8_twfe_full_correlation_matrix.xlsx
+++ b/08_tables/q8_twfe_full_correlation_matrix.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,69 +417,69 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>twfe_i</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>twfe_P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>twfe_W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>twfe_WR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>twfe_GDP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>twfe_LS</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>twfe_UN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>twfe_SHORTUN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>twfe_LONGUN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>twfe_LF</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>twfe_REER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>twfe_SH</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>twfe_i</t>
         </is>
@@ -506,13 +494,13 @@
         <v>0.1175939348588404</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03336043024836715</v>
+        <v>-0.03336043024836714</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1291895219696686</v>
+        <v>0.1291895219696687</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04544251244914864</v>
+        <v>0.04544251244914865</v>
       </c>
       <c r="H2" t="n">
         <v>-0.1903334044719837</v>
@@ -521,20 +509,20 @@
         <v>-0.1309293711529568</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.04171848529911153</v>
+        <v>-0.04171848529911155</v>
       </c>
       <c r="K2" t="n">
         <v>0.1304874601426329</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0892904873789899</v>
+        <v>-0.08929048737898987</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9342692142583985</v>
+        <v>0.9342692142583984</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>twfe_P</t>
         </is>
@@ -552,32 +540,32 @@
         <v>-0.5812401082436446</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07784078362258766</v>
+        <v>-0.07784078362258767</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2695340316059607</v>
+        <v>-0.2695340316059608</v>
       </c>
       <c r="H3" t="n">
         <v>0.1897580429186116</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009506876254764787</v>
+        <v>0.009506876254764769</v>
       </c>
       <c r="J3" t="n">
         <v>0.01084581153028091</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1365328782957384</v>
+        <v>-0.1365328782957383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2832397758252276</v>
+        <v>0.2832397758252275</v>
       </c>
       <c r="M3" t="n">
         <v>-0.2603182010849705</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>twfe_W</t>
         </is>
@@ -592,7 +580,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5375138081065493</v>
+        <v>0.5375138081065491</v>
       </c>
       <c r="F4" t="n">
         <v>0.3872661207852854</v>
@@ -604,7 +592,7 @@
         <v>-0.1155248977461527</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03848048103055679</v>
+        <v>0.03848048103055678</v>
       </c>
       <c r="J4" t="n">
         <v>0.1380009057430586</v>
@@ -613,41 +601,41 @@
         <v>0.3129643744739594</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.06169605945235788</v>
+        <v>-0.06169605945235784</v>
       </c>
       <c r="M4" t="n">
         <v>0.1354108048467415</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>twfe_WR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.03336043024836715</v>
+        <v>-0.03336043024836714</v>
       </c>
       <c r="C5" t="n">
         <v>-0.5812401082436446</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5375138081065493</v>
+        <v>0.5375138081065491</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1812992811396713</v>
+        <v>0.1812992811396712</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6229138660897947</v>
+        <v>0.6229138660897946</v>
       </c>
       <c r="H5" t="n">
         <v>-0.1000962505175084</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2213032225424325</v>
+        <v>0.2213032225424326</v>
       </c>
       <c r="J5" t="n">
         <v>0.09929771378723645</v>
@@ -659,26 +647,26 @@
         <v>-0.2600082699103004</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02031013290622618</v>
+        <v>-0.02031013290622614</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>twfe_GDP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1291895219696686</v>
+        <v>0.1291895219696687</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.07784078362258766</v>
+        <v>-0.07784078362258767</v>
       </c>
       <c r="D6" t="n">
         <v>0.3872661207852854</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1812992811396713</v>
+        <v>0.1812992811396712</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -696,32 +684,32 @@
         <v>0.3392583051447964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9509010816886672</v>
+        <v>0.9509010816886669</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0652105201359955</v>
+        <v>0.06521052013599551</v>
       </c>
       <c r="M6" t="n">
         <v>0.1450629814146986</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>twfe_LS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04544251244914864</v>
+        <v>0.04544251244914865</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2695340316059607</v>
+        <v>-0.2695340316059608</v>
       </c>
       <c r="D7" t="n">
         <v>0.4394017069477426</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6229138660897947</v>
+        <v>0.6229138660897946</v>
       </c>
       <c r="F7" t="n">
         <v>0.1843331706737057</v>
@@ -745,11 +733,11 @@
         <v>-0.14785502275517</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05832547838823485</v>
+        <v>0.05832547838823483</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>twfe_UN</t>
         </is>
@@ -776,23 +764,23 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03680821384477019</v>
+        <v>0.03680821384477015</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4247418544180811</v>
+        <v>0.4247418544180812</v>
       </c>
       <c r="K8" t="n">
         <v>-0.1721173786150877</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.01735066516419554</v>
+        <v>-0.01735066516419555</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1778535710689595</v>
+        <v>-0.1778535710689594</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>twfe_SHORTUN</t>
         </is>
@@ -801,13 +789,13 @@
         <v>-0.1309293711529568</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009506876254764787</v>
+        <v>0.009506876254764769</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03848048103055679</v>
+        <v>0.03848048103055678</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2213032225424325</v>
+        <v>0.2213032225424326</v>
       </c>
       <c r="F9" t="n">
         <v>0.2149691977180542</v>
@@ -816,7 +804,7 @@
         <v>0.06951323291868929</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03680821384477019</v>
+        <v>0.03680821384477015</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -835,13 +823,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>twfe_LONGUN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04171848529911153</v>
+        <v>-0.04171848529911155</v>
       </c>
       <c r="C10" t="n">
         <v>0.01084581153028091</v>
@@ -859,7 +847,7 @@
         <v>-0.1530513946684996</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4247418544180811</v>
+        <v>0.4247418544180812</v>
       </c>
       <c r="I10" t="n">
         <v>0.3804980672086085</v>
@@ -871,14 +859,14 @@
         <v>0.3485027996528611</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.04082890302796373</v>
+        <v>-0.04082890302796369</v>
       </c>
       <c r="M10" t="n">
         <v>-0.05282081992841844</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>twfe_LF</t>
         </is>
@@ -887,7 +875,7 @@
         <v>0.1304874601426329</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1365328782957384</v>
+        <v>-0.1365328782957383</v>
       </c>
       <c r="D11" t="n">
         <v>0.3129643744739594</v>
@@ -896,7 +884,7 @@
         <v>0.2157882268855121</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9509010816886672</v>
+        <v>0.9509010816886669</v>
       </c>
       <c r="G11" t="n">
         <v>0.1982577854039982</v>
@@ -914,63 +902,63 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06978257969736462</v>
+        <v>0.06978257969736461</v>
       </c>
       <c r="M11" t="n">
         <v>0.1384836699693837</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>twfe_REER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0892904873789899</v>
+        <v>-0.08929048737898987</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2832397758252276</v>
+        <v>0.2832397758252275</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.06169605945235788</v>
+        <v>-0.06169605945235784</v>
       </c>
       <c r="E12" t="n">
         <v>-0.2600082699103004</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0652105201359955</v>
+        <v>0.06521052013599551</v>
       </c>
       <c r="G12" t="n">
         <v>-0.14785502275517</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.01735066516419554</v>
+        <v>-0.01735066516419555</v>
       </c>
       <c r="I12" t="n">
         <v>-0.1901050286194512</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.04082890302796373</v>
+        <v>-0.04082890302796369</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06978257969736462</v>
+        <v>0.06978257969736461</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.08957053628998134</v>
+        <v>-0.08957053628998132</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>twfe_SH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9342692142583985</v>
+        <v>0.9342692142583984</v>
       </c>
       <c r="C13" t="n">
         <v>-0.2603182010849705</v>
@@ -979,16 +967,16 @@
         <v>0.1354108048467415</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.02031013290622618</v>
+        <v>-0.02031013290622614</v>
       </c>
       <c r="F13" t="n">
         <v>0.1450629814146986</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05832547838823485</v>
+        <v>0.05832547838823483</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1778535710689595</v>
+        <v>-0.1778535710689594</v>
       </c>
       <c r="I13" t="n">
         <v>-0.1308708000007529</v>
@@ -1000,7 +988,7 @@
         <v>0.1384836699693837</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.08957053628998134</v>
+        <v>-0.08957053628998132</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
